--- a/dynamical_DE_nonfid/cmb/highl_litebird_fisher.xlsx
+++ b/dynamical_DE_nonfid/cmb/highl_litebird_fisher.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,34 +487,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5034018.944175494</v>
+        <v>1512173.413240713</v>
       </c>
       <c r="C2" t="n">
-        <v>-8162408.469695398</v>
+        <v>-2453887.170611492</v>
       </c>
       <c r="D2" t="n">
-        <v>4341302.776828061</v>
+        <v>1303591.462189209</v>
       </c>
       <c r="E2" t="n">
-        <v>765028.2716469181</v>
+        <v>230677.7151959627</v>
       </c>
       <c r="F2" t="n">
-        <v>-1878358.280181239</v>
+        <v>-564487.1116523605</v>
       </c>
       <c r="G2" t="n">
-        <v>-508756.9313444357</v>
+        <v>-152899.6014829128</v>
       </c>
       <c r="H2" t="n">
-        <v>-164292.1404276924</v>
+        <v>-49342.41779135669</v>
       </c>
       <c r="I2" t="n">
-        <v>1512813.80867067</v>
+        <v>454579.8711859273</v>
       </c>
       <c r="J2" t="n">
-        <v>-279902.8244535986</v>
+        <v>-84200.02480946577</v>
       </c>
       <c r="K2" t="n">
-        <v>-78127.33629333404</v>
+        <v>-23499.77156209116</v>
       </c>
     </row>
     <row r="3">
@@ -524,34 +524,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-8162408.469695398</v>
+        <v>-2453887.170611492</v>
       </c>
       <c r="C3" t="n">
-        <v>26205118.34000696</v>
+        <v>7875170.013067062</v>
       </c>
       <c r="D3" t="n">
-        <v>-6160122.457771357</v>
+        <v>-1851202.735113044</v>
       </c>
       <c r="E3" t="n">
-        <v>-1136735.104775432</v>
+        <v>-344033.0969120192</v>
       </c>
       <c r="F3" t="n">
-        <v>2630818.689925786</v>
+        <v>791785.4482809436</v>
       </c>
       <c r="G3" t="n">
-        <v>632806.2272469677</v>
+        <v>190547.1174145304</v>
       </c>
       <c r="H3" t="n">
-        <v>319416.6826974557</v>
+        <v>95970.65018230086</v>
       </c>
       <c r="I3" t="n">
-        <v>-2122842.798328192</v>
+        <v>-638754.4801187242</v>
       </c>
       <c r="J3" t="n">
-        <v>72029.51345685167</v>
+        <v>22195.56777337979</v>
       </c>
       <c r="K3" t="n">
-        <v>29720.1495328148</v>
+        <v>9073.938755714638</v>
       </c>
     </row>
     <row r="4">
@@ -561,34 +561,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4341302.776828061</v>
+        <v>1303591.462189209</v>
       </c>
       <c r="C4" t="n">
-        <v>-6160122.457771357</v>
+        <v>-1851202.735113044</v>
       </c>
       <c r="D4" t="n">
-        <v>3850814.528363644</v>
+        <v>1155984.599593111</v>
       </c>
       <c r="E4" t="n">
-        <v>640224.6915811416</v>
+        <v>192775.2221961126</v>
       </c>
       <c r="F4" t="n">
-        <v>-1605831.761832348</v>
+        <v>-482344.2148198925</v>
       </c>
       <c r="G4" t="n">
-        <v>-437089.4237257323</v>
+        <v>-131291.6130776712</v>
       </c>
       <c r="H4" t="n">
-        <v>-141784.9801874133</v>
+        <v>-42569.39607302117</v>
       </c>
       <c r="I4" t="n">
-        <v>1293172.712253086</v>
+        <v>388397.1286937126</v>
       </c>
       <c r="J4" t="n">
-        <v>-243704.4815669777</v>
+        <v>-73247.74785989683</v>
       </c>
       <c r="K4" t="n">
-        <v>-67887.66111875571</v>
+        <v>-20402.98404636551</v>
       </c>
     </row>
     <row r="5">
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>765028.2716469181</v>
+        <v>230677.7151959627</v>
       </c>
       <c r="C5" t="n">
-        <v>-1136735.104775432</v>
+        <v>-344033.0969120192</v>
       </c>
       <c r="D5" t="n">
-        <v>640224.6915811416</v>
+        <v>192775.2221961126</v>
       </c>
       <c r="E5" t="n">
-        <v>152693.6405522301</v>
+        <v>46553.53469242175</v>
       </c>
       <c r="F5" t="n">
-        <v>-308407.0528393302</v>
+        <v>-93132.47134457645</v>
       </c>
       <c r="G5" t="n">
-        <v>-86014.45094844636</v>
+        <v>-25974.62454390419</v>
       </c>
       <c r="H5" t="n">
-        <v>-23192.3032138454</v>
+        <v>-6988.987300161964</v>
       </c>
       <c r="I5" t="n">
-        <v>247748.2643871244</v>
+        <v>74787.7491684665</v>
       </c>
       <c r="J5" t="n">
-        <v>-57782.37423353252</v>
+        <v>-17481.74666031613</v>
       </c>
       <c r="K5" t="n">
-        <v>-15773.26295678573</v>
+        <v>-4771.409331573279</v>
       </c>
     </row>
     <row r="6">
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1878358.280181239</v>
+        <v>-564487.1116523605</v>
       </c>
       <c r="C6" t="n">
-        <v>2630818.689925786</v>
+        <v>791785.4482809437</v>
       </c>
       <c r="D6" t="n">
-        <v>-1605831.761832347</v>
+        <v>-482344.2148198926</v>
       </c>
       <c r="E6" t="n">
-        <v>-308407.0528393302</v>
+        <v>-93132.47134457644</v>
       </c>
       <c r="F6" t="n">
-        <v>772541.9324191378</v>
+        <v>232266.0769659559</v>
       </c>
       <c r="G6" t="n">
-        <v>214034.9534740334</v>
+        <v>64350.82283298436</v>
       </c>
       <c r="H6" t="n">
-        <v>55319.91634450875</v>
+        <v>16622.54719176193</v>
       </c>
       <c r="I6" t="n">
-        <v>-621803.891274569</v>
+        <v>-186921.9925006951</v>
       </c>
       <c r="J6" t="n">
-        <v>142934.0958595166</v>
+        <v>43000.34527558243</v>
       </c>
       <c r="K6" t="n">
-        <v>39061.58000062841</v>
+        <v>11750.69346818733</v>
       </c>
     </row>
     <row r="7">
@@ -672,34 +672,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-508756.9313444357</v>
+        <v>-152899.6014829128</v>
       </c>
       <c r="C7" t="n">
-        <v>632806.2272469677</v>
+        <v>190547.1174145304</v>
       </c>
       <c r="D7" t="n">
-        <v>-437089.4237257323</v>
+        <v>-131291.6130776712</v>
       </c>
       <c r="E7" t="n">
-        <v>-86014.45094844636</v>
+        <v>-25974.62454390419</v>
       </c>
       <c r="F7" t="n">
-        <v>214034.9534740334</v>
+        <v>64350.82283298437</v>
       </c>
       <c r="G7" t="n">
-        <v>60006.93968747995</v>
+        <v>18041.2525640235</v>
       </c>
       <c r="H7" t="n">
-        <v>14431.36784757465</v>
+        <v>4336.760865717586</v>
       </c>
       <c r="I7" t="n">
-        <v>-172255.9004688654</v>
+        <v>-51783.02031374566</v>
       </c>
       <c r="J7" t="n">
-        <v>42515.74535632598</v>
+        <v>12788.43223409355</v>
       </c>
       <c r="K7" t="n">
-        <v>11548.6295584216</v>
+        <v>3473.625894760129</v>
       </c>
     </row>
     <row r="8">
@@ -709,34 +709,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-164292.1404276924</v>
+        <v>-49342.41779135669</v>
       </c>
       <c r="C8" t="n">
-        <v>319416.6826974557</v>
+        <v>95970.65018230086</v>
       </c>
       <c r="D8" t="n">
-        <v>-141784.9801874133</v>
+        <v>-42569.39607302118</v>
       </c>
       <c r="E8" t="n">
-        <v>-23192.3032138454</v>
+        <v>-6988.987300161964</v>
       </c>
       <c r="F8" t="n">
-        <v>55319.91634450875</v>
+        <v>16622.54719176193</v>
       </c>
       <c r="G8" t="n">
-        <v>14431.36784757465</v>
+        <v>4336.760865717586</v>
       </c>
       <c r="H8" t="n">
-        <v>5934.087747089095</v>
+        <v>1781.799511581263</v>
       </c>
       <c r="I8" t="n">
-        <v>-44570.90357198716</v>
+        <v>-13391.07196186807</v>
       </c>
       <c r="J8" t="n">
-        <v>5481.96238883748</v>
+        <v>1650.590324573353</v>
       </c>
       <c r="K8" t="n">
-        <v>1612.863919734376</v>
+        <v>485.4763232018307</v>
       </c>
     </row>
     <row r="9">
@@ -746,34 +746,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1512813.80867067</v>
+        <v>454579.8711859274</v>
       </c>
       <c r="C9" t="n">
-        <v>-2122842.798328192</v>
+        <v>-638754.4801187242</v>
       </c>
       <c r="D9" t="n">
-        <v>1293172.712253086</v>
+        <v>388397.1286937126</v>
       </c>
       <c r="E9" t="n">
-        <v>247748.2643871244</v>
+        <v>74787.7491684665</v>
       </c>
       <c r="F9" t="n">
-        <v>-621803.891274569</v>
+        <v>-186921.9925006951</v>
       </c>
       <c r="G9" t="n">
-        <v>-172255.9004688654</v>
+        <v>-51783.02031374566</v>
       </c>
       <c r="H9" t="n">
-        <v>-44570.90357198716</v>
+        <v>-13391.07196186807</v>
       </c>
       <c r="I9" t="n">
-        <v>500585.0230651773</v>
+        <v>150464.2052417984</v>
       </c>
       <c r="J9" t="n">
-        <v>-114900.6532257119</v>
+        <v>-34561.6598094532</v>
       </c>
       <c r="K9" t="n">
-        <v>-31404.55296219137</v>
+        <v>-9445.883849214453</v>
       </c>
     </row>
     <row r="10">
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-279902.8244535986</v>
+        <v>-84200.02480946577</v>
       </c>
       <c r="C10" t="n">
-        <v>72029.51345685165</v>
+        <v>22195.56777337979</v>
       </c>
       <c r="D10" t="n">
-        <v>-243704.4815669777</v>
+        <v>-73247.74785989683</v>
       </c>
       <c r="E10" t="n">
-        <v>-57782.37423353253</v>
+        <v>-17481.74666031613</v>
       </c>
       <c r="F10" t="n">
-        <v>142934.0958595166</v>
+        <v>43000.34527558243</v>
       </c>
       <c r="G10" t="n">
-        <v>42515.74535632598</v>
+        <v>12788.43223409355</v>
       </c>
       <c r="H10" t="n">
-        <v>5481.96238883748</v>
+        <v>1650.590324573353</v>
       </c>
       <c r="I10" t="n">
-        <v>-114900.6532257119</v>
+        <v>-34561.6598094532</v>
       </c>
       <c r="J10" t="n">
-        <v>39875.5128702156</v>
+        <v>11992.36490371395</v>
       </c>
       <c r="K10" t="n">
-        <v>10573.20536108973</v>
+        <v>3179.909830182285</v>
       </c>
     </row>
     <row r="11">
@@ -820,34 +820,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-78127.33629333405</v>
+        <v>-23499.77156209116</v>
       </c>
       <c r="C11" t="n">
-        <v>29720.14953281479</v>
+        <v>9073.938755714636</v>
       </c>
       <c r="D11" t="n">
-        <v>-67887.6611187557</v>
+        <v>-20402.98404636551</v>
       </c>
       <c r="E11" t="n">
-        <v>-15773.26295678573</v>
+        <v>-4771.409331573279</v>
       </c>
       <c r="F11" t="n">
-        <v>39061.58000062841</v>
+        <v>11750.69346818733</v>
       </c>
       <c r="G11" t="n">
-        <v>11548.6295584216</v>
+        <v>3473.625894760128</v>
       </c>
       <c r="H11" t="n">
-        <v>1612.863919734376</v>
+        <v>485.4763232018307</v>
       </c>
       <c r="I11" t="n">
-        <v>-31404.55296219137</v>
+        <v>-9445.883849214453</v>
       </c>
       <c r="J11" t="n">
-        <v>10573.20536108973</v>
+        <v>3179.909830182285</v>
       </c>
       <c r="K11" t="n">
-        <v>2808.734327786769</v>
+        <v>844.7470209000901</v>
       </c>
     </row>
   </sheetData>
